--- a/outputs/Block5B_Senate_Specification_Folds.xlsx
+++ b/outputs/Block5B_Senate_Specification_Folds.xlsx
@@ -43,10 +43,10 @@
     <t>Outer Selected MAE PP</t>
   </si>
   <si>
+    <t>PooledPollStructure</t>
+  </si>
+  <si>
     <t>PooledFullV11</t>
-  </si>
-  <si>
-    <t>PooledPollStructure</t>
   </si>
 </sst>
 </file>
@@ -444,25 +444,25 @@
         <v>9</v>
       </c>
       <c r="C2">
+        <v>4</v>
+      </c>
+      <c r="D2">
         <v>0.25</v>
       </c>
-      <c r="D2">
-        <v>0</v>
-      </c>
       <c r="E2">
-        <v>1</v>
+        <v>0.75</v>
       </c>
       <c r="F2">
         <v>4.924645547677709</v>
       </c>
       <c r="G2">
-        <v>4.209288146226513</v>
+        <v>4.740007554617968</v>
       </c>
       <c r="H2">
         <v>5.579313654851505</v>
       </c>
       <c r="I2">
-        <v>3.685780746769227</v>
+        <v>5.604575353223307</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -473,7 +473,7 @@
         <v>9</v>
       </c>
       <c r="C3">
-        <v>100</v>
+        <v>0.25</v>
       </c>
       <c r="D3">
         <v>1</v>
@@ -499,7 +499,7 @@
         <v>2014</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>0.25</v>
@@ -528,28 +528,28 @@
         <v>2018</v>
       </c>
       <c r="B5" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C5">
         <v>0.25</v>
       </c>
       <c r="D5">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="E5">
-        <v>0.75</v>
+        <v>0.5</v>
       </c>
       <c r="F5">
         <v>5.365909389316474</v>
       </c>
       <c r="G5">
-        <v>4.497328544976817</v>
+        <v>5.017857937181216</v>
       </c>
       <c r="H5">
         <v>3.659578902902788</v>
       </c>
       <c r="I5">
-        <v>4.098446160475629</v>
+        <v>3.878601788930343</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -557,7 +557,7 @@
         <v>2022</v>
       </c>
       <c r="B6" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C6">
         <v>1</v>
